--- a/docs/harness/wirelist/CabinPower-pinouts.xlsx
+++ b/docs/harness/wirelist/CabinPower-pinouts.xlsx
@@ -2110,7 +2110,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>BULKHEAD pin 42</t>
+          <t>BULKHEAD pin 83</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>BULKHEAD pin 2</t>
+          <t>BULKHEAD pin 1</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>BULKHEAD pin 1</t>
+          <t>BULKHEAD pin 2</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>BULKHEAD pin 56</t>
+          <t>BULKHEAD pin 85</t>
         </is>
       </c>
     </row>
